--- a/results/Int All Data 0.6/Rando_1_permute.xlsx
+++ b/results/Int All Data 0.6/Rando_1_permute.xlsx
@@ -440,107 +440,107 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9445606694560669</v>
+        <v>0.9424686192468619</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9445606694560669</v>
+        <v>0.9424686192468619</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9435146443514644</v>
+        <v>0.9424686192468619</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9435146443514644</v>
+        <v>0.9131799163179917</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9435146443514644</v>
+        <v>0.9152719665271967</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9435146443514644</v>
+        <v>0.9131799163179917</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9445606694560669</v>
+        <v>0.9173640167364017</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9445606694560669</v>
+        <v>0.9173640167364017</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9445606694560669</v>
+        <v>0.9330543933054394</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9424686192468619</v>
+        <v>0.9278242677824268</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9403765690376569</v>
+        <v>0.9278242677824268</v>
       </c>
     </row>
     <row r="13">
@@ -550,887 +550,887 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9403765690376569</v>
+        <v>0.9278242677824268</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9435146443514644</v>
+        <v>0.9278242677824268</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9435146443514644</v>
+        <v>0.9225941422594142</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.943175661300617</v>
+        <v>0.891213389121339</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.943175661300617</v>
+        <v>0.891213389121339</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9442216864052195</v>
+        <v>0.9100418410041842</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9414225941422594</v>
+        <v>0.9079497907949791</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9414225941422594</v>
+        <v>0.9131799163179917</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9414225941422594</v>
+        <v>0.9131799163179917</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9445606694560669</v>
+        <v>0.9121338912133892</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9445606694560669</v>
+        <v>0.9131799163179917</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9445606694560669</v>
+        <v>0.9131799163179917</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9445606694560669</v>
+        <v>0.9163179916317992</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9445606694560669</v>
+        <v>0.9163179916317992</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.9445606694560669</v>
+        <v>0.9131799163179917</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.9445606694560669</v>
+        <v>0.9069037656903766</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.9435437203035246</v>
+        <v>0.9142259414225942</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.9435437203035246</v>
+        <v>0.9163179916317992</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.9432047372526771</v>
+        <v>0.9152719665271967</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.9435437203035246</v>
+        <v>0.9100418410041842</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.9432047372526771</v>
+        <v>0.9173640167364017</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.9432047372526771</v>
+        <v>0.9121338912133892</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.9435437203035246</v>
+        <v>0.9079497907949791</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.9435437203035246</v>
+        <v>0.9006276150627615</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.9435727962555847</v>
+        <v>0.9069037656903766</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.9435727962555847</v>
+        <v>0.9069037656903766</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.9456357705127296</v>
+        <v>0.9079497907949791</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.9456357705127296</v>
+        <v>0.9058577405857741</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.9456357705127296</v>
+        <v>0.9121338912133892</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.9456357705127296</v>
+        <v>0.9121338912133892</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.9459747535635771</v>
+        <v>0.9215481171548117</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.9463137366144245</v>
+        <v>0.9215481171548117</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.9463137366144245</v>
+        <v>0.9236401673640167</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.9463137366144245</v>
+        <v>0.9247152684206794</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.9463137366144245</v>
+        <v>0.9324345791078648</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.9442216864052195</v>
+        <v>0.9306815119495071</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.9435437203035246</v>
+        <v>0.9317275370541096</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.9414807460463797</v>
+        <v>0.9317275370541096</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.9411708389475923</v>
+        <v>0.9268363945819444</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.9411708389475923</v>
+        <v>0.9275143606836395</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.9411708389475923</v>
+        <v>0.9278533437344869</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.9367349833345153</v>
+        <v>0.9191461598468194</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.9360570172328204</v>
+        <v>0.9153010424792568</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.9360860931848805</v>
+        <v>0.9173930926884618</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.9374420253882703</v>
+        <v>0.9173930926884618</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.9314275583291964</v>
+        <v>0.9173930926884618</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.9310885752783491</v>
+        <v>0.9037947663286292</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.9310885752783491</v>
+        <v>0.876598113608964</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.9276987447698745</v>
+        <v>0.8800751719736188</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.926652719665272</v>
+        <v>0.8790291468690163</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.926652719665272</v>
+        <v>0.8769661726118716</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.926652719665272</v>
+        <v>0.8832423232394866</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.9246188213601872</v>
+        <v>0.8850244663499043</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.9263137366144245</v>
+        <v>0.8780412736685341</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.927330685766967</v>
+        <v>0.8449365293241614</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.9293645840720517</v>
+        <v>0.8717941989929792</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.9232628891567973</v>
+        <v>0.8717941989929792</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.9219069569534075</v>
+        <v>0.8766853414651443</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.92295298205801</v>
+        <v>0.8491787816466917</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.9205801007020779</v>
+        <v>0.8477937734912417</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.9205801007020779</v>
+        <v>0.8477937734912417</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.9178682362952982</v>
+        <v>0.8401326147081767</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.9198730586483228</v>
+        <v>0.8383795475498191</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.92295298205801</v>
+        <v>0.8380114885469117</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.9232919651088576</v>
+        <v>0.8337983121764414</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.9243089142613998</v>
+        <v>0.8226310190766613</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.9232919651088576</v>
+        <v>0.836035742145947</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.9232919651088576</v>
+        <v>0.8393191972200553</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.92295298205801</v>
+        <v>0.8467576767605134</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.919224168498688</v>
+        <v>0.8530338273881285</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.9243089142613998</v>
+        <v>0.8499730515566272</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.9243089142613998</v>
+        <v>0.845759875186157</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.9243089142613998</v>
+        <v>0.845052833132402</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.9236309481597049</v>
+        <v>0.845052833132402</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.9263137366144245</v>
+        <v>0.8524913126728602</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.9243089142613998</v>
+        <v>0.8556293879866677</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.9222168640521948</v>
+        <v>0.8552613289837601</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.9219360329054678</v>
+        <v>0.8552613289837601</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.9293645840720517</v>
+        <v>0.85384724487625</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.9293645840720517</v>
+        <v>0.8507382455145025</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.9304106091766542</v>
+        <v>0.8507382455145025</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.922972129636196</v>
+        <v>0.7893617473938019</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.9148847599461032</v>
+        <v>0.7959768810722644</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.9101389972342387</v>
+        <v>0.7977008722785618</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.9164151478618539</v>
+        <v>0.7938848308630593</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.9146911566555563</v>
+        <v>0.7772065810935395</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.9137032834550741</v>
+        <v>0.7418062548755407</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.9120083682008369</v>
+        <v>0.7414672718246933</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.8955045741436778</v>
+        <v>0.7404212467200908</v>
       </c>
     </row>
     <row r="102">
@@ -1440,547 +1440,547 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.9035337919296504</v>
+        <v>0.7574675554925183</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.8707588114318133</v>
+        <v>0.7393752216154883</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.869741862279271</v>
+        <v>0.7582909013545138</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.8714367775335082</v>
+        <v>0.7579228423516062</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.8562499113538047</v>
+        <v>0.767821431104177</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.8559109283029572</v>
+        <v>0.7668044819516346</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.8389128430607758</v>
+        <v>0.7668044819516346</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.8389128430607758</v>
+        <v>0.7729742571448833</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.8335664137295227</v>
+        <v>0.7685674774838664</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.8429806396709454</v>
+        <v>0.723752925324445</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.8443365718743352</v>
+        <v>0.6048450464506063</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.8235614495425856</v>
+        <v>0.6109275937876747</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.8235614495425856</v>
+        <v>0.6570881497766116</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.8253145167009432</v>
+        <v>0.5822877810084391</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.766824338699383</v>
+        <v>0.5759244025246436</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.763773491241756</v>
+        <v>0.6058329196510885</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.7633182043826678</v>
+        <v>0.5437493794766328</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.7563059357492377</v>
+        <v>0.5437493794766328</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.7622431033260053</v>
+        <v>0.6009226296007375</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.7296709453230268</v>
+        <v>0.5845542869300049</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.7520346074746471</v>
+        <v>0.5845542869300049</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.7478505070562371</v>
+        <v>0.5845542869300049</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.7420778668179562</v>
+        <v>0.5713821714772003</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.7423877739167435</v>
+        <v>0.5737550528331323</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.7525090419119211</v>
+        <v>0.6057364725905965</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.753187008013616</v>
+        <v>0.6279547549819162</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.6996943479185873</v>
+        <v>0.7016417275370541</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.6941252393447274</v>
+        <v>0.6497957591660166</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.6941252393447274</v>
+        <v>0.6451854478405787</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.6920041131834622</v>
+        <v>0.6498248351180768</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.6832969292957947</v>
+        <v>0.6498248351180768</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.6516452733848663</v>
+        <v>0.6494858520672293</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.6481391390681512</v>
+        <v>0.67052265796752</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.6682263669243316</v>
+        <v>0.67052265796752</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.6993943691936741</v>
+        <v>0.6143472094177718</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.6809439046876108</v>
+        <v>0.5781136089639033</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.6892830295723708</v>
+        <v>0.5416282533153677</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.7506694560669456</v>
+        <v>0.5416282533153677</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.7675413091270122</v>
+        <v>0.5450570881497766</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.7589419190128359</v>
+        <v>0.5457059782994114</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.6193943691936742</v>
+        <v>0.5430813417488122</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.6338550457414367</v>
+        <v>0.5416963335933622</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.6323246578256861</v>
+        <v>0.5821232536699524</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.6105233671370824</v>
+        <v>0.5585391107013686</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.6105233671370824</v>
+        <v>0.5219863839444011</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.5955400326217999</v>
+        <v>0.5219863839444011</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5955400326217999</v>
+        <v>0.5223253669952486</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.6052648748315722</v>
+        <v>0.5139862421104886</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5126870434720942</v>
+        <v>0.5176569037656904</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5126870434720942</v>
+        <v>0.5121168711438905</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.5060236862633856</v>
+        <v>0.5121168711438905</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.4941692078575988</v>
+        <v>0.5121168711438905</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.4941692078575988</v>
+        <v>0.5113034536557691</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.4957286717254096</v>
+        <v>0.497821431104177</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.4974817388837671</v>
+        <v>0.4944316005957025</v>
       </c>
     </row>
   </sheetData>
